--- a/Produtos/Tabela_Produtos.xlsx
+++ b/Produtos/Tabela_Produtos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\caieb\OneDrive\Documentos\Meus Projetos - GitGitHub\Automacao_Web_Buscador_de_melhores_precos\Produtos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{613AC47A-71BF-4F1C-B055-59446E92FADD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DC7B5A0-2ACA-4A60-8B04-22D9F0F61AD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4188" yWindow="4188" windowWidth="30960" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -51,7 +51,7 @@
     <t>Himalayan 411</t>
   </si>
   <si>
-    <t>9060XT, 9060, 5070</t>
+    <t>9060XT 9060 5070</t>
   </si>
 </sst>
 </file>

--- a/Produtos/Tabela_Produtos.xlsx
+++ b/Produtos/Tabela_Produtos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\caieb\OneDrive\Documentos\Meus Projetos - GitGitHub\Automacao_Web_Buscador_de_melhores_precos\Produtos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DC7B5A0-2ACA-4A60-8B04-22D9F0F61AD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68042C07-31A6-4106-9852-6941383391FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4188" yWindow="4188" windowWidth="30960" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,16 +42,16 @@
     <t>Preço Max</t>
   </si>
   <si>
-    <t>RX 9070XT</t>
-  </si>
-  <si>
     <t>Himalayan 450</t>
   </si>
   <si>
     <t>Himalayan 411</t>
   </si>
   <si>
-    <t>9060XT 9060 5070</t>
+    <t>RX 9070 XT</t>
+  </si>
+  <si>
+    <t>9060 XT 9060 5070</t>
   </si>
 </sst>
 </file>
@@ -396,7 +396,7 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
@@ -410,10 +410,10 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
         <v>5</v>
-      </c>
-      <c r="B3" t="s">
-        <v>6</v>
       </c>
       <c r="C3" s="1">
         <v>29000</v>

--- a/Produtos/Tabela_Produtos.xlsx
+++ b/Produtos/Tabela_Produtos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\caieb\OneDrive\Documentos\Meus Projetos - GitGitHub\Automacao_Web_Buscador_de_melhores_precos\Produtos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68042C07-31A6-4106-9852-6941383391FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFA03498-D91F-4FCA-B053-9521EC65C891}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4188" yWindow="4188" windowWidth="30960" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -405,7 +405,7 @@
         <v>3800</v>
       </c>
       <c r="D2" s="1">
-        <v>4500</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">

--- a/Produtos/Tabela_Produtos.xlsx
+++ b/Produtos/Tabela_Produtos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\caieb\OneDrive\Documentos\Meus Projetos - GitGitHub\Automacao_Web_Buscador_de_melhores_precos\Produtos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFA03498-D91F-4FCA-B053-9521EC65C891}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{270F94F6-7866-452A-893E-B072C52815A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4188" yWindow="4188" windowWidth="30960" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -58,9 +58,6 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="&quot;R$&quot;\ #,##0.00"/>
-  </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -92,7 +89,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -405,7 +402,7 @@
         <v>3800</v>
       </c>
       <c r="D2" s="1">
-        <v>5200</v>
+        <v>5500</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
